--- a/workspace/framework_paper/edf-local/gradient_edf_local_eval_schedulables.xlsx
+++ b/workspace/framework_paper/edf-local/gradient_edf_local_eval_schedulables.xlsx
@@ -466,7 +466,7 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" t="n">
         <v>50</v>
@@ -480,7 +480,7 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
         <v>50</v>
@@ -494,10 +494,10 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C6" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
         <v>50</v>
@@ -508,10 +508,10 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D7" t="n">
         <v>50</v>
@@ -522,10 +522,10 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">

--- a/workspace/framework_paper/edf-local/gradient_edf_local_eval_schedulables.xlsx
+++ b/workspace/framework_paper/edf-local/gradient_edf_local_eval_schedulables.xlsx
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17">
@@ -648,13 +648,13 @@
         <v>0.8157894736842105</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
@@ -662,13 +662,13 @@
         <v>0.8368421052631578</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -676,13 +676,13 @@
         <v>0.8578947368421053</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -690,13 +690,13 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -704,13 +704,13 @@
         <v>0.9</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
